--- a/src/test/resources/testdata/DailyJobs_UpdatedHourly.xlsx
+++ b/src/test/resources/testdata/DailyJobs_UpdatedHourly.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="254">
   <si>
     <t>Last Hour Job Search Results</t>
   </si>
@@ -756,6 +756,24 @@
   </si>
   <si>
     <t>https://www.linkedin.com/jobs/view/4436931443/</t>
+  </si>
+  <si>
+    <t>Manager | Audit | Audit &amp; Assurance | UAE FY27 | Deloitte | Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4389089317/</t>
+  </si>
+  <si>
+    <t>Job Description – QA Engineer (Manual &amp; Automation Testing) | Unicorn Lab | Dubai, Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433735887/</t>
+  </si>
+  <si>
+    <t>QA/QC Engineers- 5+ Years of Experience- High Rise Buildings Mandatory- Contracting Background | Auxilium | Dubai, Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433751438/</t>
   </si>
 </sst>
 </file>
@@ -800,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B137"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1869,6 +1887,35 @@
         <v>247</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
